--- a/data/trans_camb/IP1019-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1019-Estudios-trans_camb.xlsx
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,0</t>
+          <t>-0,86; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,0</t>
+          <t>-0,83; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,0</t>
+          <t>-0,45; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -953,17 +953,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 0,0</t>
+          <t>-2,13; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,0</t>
+          <t>-2,14; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,0</t>
+          <t>-1,22; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,0</t>
+          <t>-0,51; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,0</t>
+          <t>-0,51; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,0</t>
+          <t>-0,34; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,0</t>
+          <t>-0,39; 0,0</t>
         </is>
       </c>
     </row>
